--- a/backend/data/financials_by_company/14N1.F.xlsx
+++ b/backend/data/financials_by_company/14N1.F.xlsx
@@ -620,13 +620,17 @@
         <v>46022</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-1597240</v>
       </c>
       <c r="C2" t="n">
         <v>0.1094</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>-14600000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-14600000</v>
+      </c>
       <c r="F2" t="n">
         <v>681446000</v>
       </c>
@@ -643,7 +647,7 @@
         <v>1874315000</v>
       </c>
       <c r="K2" t="n">
-        <v>681446000</v>
+        <v>694448760</v>
       </c>
       <c r="L2" t="n">
         <v>681446000</v>
@@ -687,10 +691,14 @@
       <c r="Y2" t="n">
         <v>806383000</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>-14600000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>13900000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>103759000</v>
+        <v>104459000</v>
       </c>
       <c r="AC2" t="n">
         <v>107477000</v>
@@ -699,22 +707,22 @@
         <v>107477000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1632524000</v>
+        <v>1618624000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1632524000</v>
+        <v>1618624000</v>
       </c>
       <c r="AG2" t="n">
-        <v>313645000</v>
+        <v>299745000</v>
       </c>
       <c r="AH2" t="n">
         <v>1318879000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2870709000</v>
+        <v>2871409000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2870709000</v>
+        <v>2871409000</v>
       </c>
       <c r="AK2" t="n">
         <v>187805000</v>
@@ -846,13 +854,17 @@
         <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-5339670</v>
       </c>
       <c r="C4" t="n">
         <v>0.1623</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>-32900000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-32900000</v>
+      </c>
       <c r="F4" t="n">
         <v>622257000</v>
       </c>
@@ -869,7 +881,7 @@
         <v>1616189000</v>
       </c>
       <c r="K4" t="n">
-        <v>622257000</v>
+        <v>649817330</v>
       </c>
       <c r="L4" t="n">
         <v>622257000</v>
@@ -913,8 +925,12 @@
       <c r="Y4" t="n">
         <v>752833000</v>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>-32900000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>32900000</v>
+      </c>
       <c r="AB4" t="n">
         <v>-9755000</v>
       </c>
@@ -925,13 +941,13 @@
         <v>80681000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1022399000</v>
+        <v>989499000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1022399000</v>
+        <v>989499000</v>
       </c>
       <c r="AG4" t="n">
-        <v>235307000</v>
+        <v>202407000</v>
       </c>
       <c r="AH4" t="n">
         <v>787092000</v>
@@ -1073,12 +1089,8 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>623000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>623000</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -1099,9 +1111,7 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
-        <v>3502000</v>
-      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>-4987000</v>
       </c>
@@ -3543,232 +3553,232 @@
       </c>
       <c r="AO1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>financialCurrency</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>sharesOutstanding</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>impliedSharesOutstanding</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>bookValue</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>marketCap</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>financialCurrency</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>sharesOutstanding</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>impliedSharesOutstanding</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>bookValue</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="CG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="CH1" t="inlineStr">
-        <is>
-          <t>marketCap</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
@@ -3785,55 +3795,55 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>7.816</v>
+        <v>7.905</v>
       </c>
       <c r="D2" t="n">
-        <v>7.805</v>
+        <v>7.965</v>
       </c>
       <c r="E2" t="n">
-        <v>7.805</v>
+        <v>7.965</v>
       </c>
       <c r="F2" t="n">
         <v>7.965</v>
       </c>
       <c r="G2" t="n">
-        <v>7.816</v>
+        <v>7.905</v>
       </c>
       <c r="H2" t="n">
-        <v>7.805</v>
+        <v>7.965</v>
       </c>
       <c r="I2" t="n">
-        <v>7.805</v>
+        <v>7.965</v>
       </c>
       <c r="J2" t="n">
         <v>7.965</v>
       </c>
       <c r="K2" t="n">
-        <v>8.457447</v>
+        <v>8.384211000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7041416</v>
+        <v>4.7130175</v>
       </c>
       <c r="M2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="N2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="O2" t="n">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="P2" t="n">
-        <v>797</v>
+        <v>265</v>
       </c>
       <c r="Q2" t="n">
-        <v>797</v>
+        <v>265</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>8.005000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -3854,16 +3864,16 @@
         <v>2.7955</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.225300000000001</v>
+        <v>8.15718</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.148505</v>
+        <v>8.961555000000001</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.12794268</v>
+        <v>0.12650222</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -3913,170 +3923,170 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.7144296</v>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Rithm Capital Corp.           R</t>
+        </is>
       </c>
       <c r="AP2" t="n">
-        <v>7.95</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
+        <v>0.7590125</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.965</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AS2" t="n">
+        <v>1782108602</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>finmb_225838735</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="AZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1493013600000</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.059999943</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>7.965 - 7.965</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>346</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.08811474599999999</v>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>7.32 - 10.815</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>-2.8499994</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-0.26352283</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>-18.252325</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1777352400</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1785214800</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1785214800</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1777377600</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1777377600</v>
+      </c>
+      <c r="BS2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>558306597</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>558306597</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>10.902275</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>-0.19217968</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>-0.023559574</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>-0.9965544</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>-0.11120329</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>4446912512</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.73058146</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="CG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH2" t="inlineStr">
         <is>
           <t>Rithm Capital Corp.</t>
         </is>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.74045736</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AW2" t="n">
-        <v>1780430102</v>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>finmb_225838735</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="BB2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="BD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>Rithm Capital Corp.           R</t>
-        </is>
-      </c>
-      <c r="BF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>1493013600000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.13399982</v>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>7.805 - 7.965</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>332</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.62999964</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.08606552000000001</v>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>7.32 - 10.815</t>
-        </is>
-      </c>
-      <c r="BP2" t="n">
-        <v>-2.8649998</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-0.26490983</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>-20.68196</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1777352400</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1785214800</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1785214800</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1777377600</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>1777377600</v>
-      </c>
-      <c r="BX2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>558306597</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>558306597</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>10.736608</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>-0.27530003</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>-0.033469908</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>-1.1985054</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>-0.1310056</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>4438537728</v>
       </c>
       <c r="CI2" t="inlineStr"/>
     </row>
